--- a/data3.xlsx
+++ b/data3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivek\wipro\wiproprogramming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67867C63-A896-41F5-8A57-6B5C4C3A7A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CA8B55-3404-4A47-9C15-A5971C7019B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{2240DF42-4699-4AAE-928F-9FBB6DBCDE1A}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>tomsmith</t>
   </si>
@@ -50,6 +50,18 @@
   </si>
   <si>
     <t>admin123</t>
+  </si>
+  <si>
+    <t>hema</t>
+  </si>
+  <si>
+    <t>welcome</t>
+  </si>
+  <si>
+    <t>geeta</t>
+  </si>
+  <si>
+    <t>apple</t>
   </si>
 </sst>
 </file>
@@ -430,7 +442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470BAF4D-A1E3-4075-A4E1-A8EFC8751857}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,6 +453,22 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
